--- a/QSExt/Resource/AKShareDBInfo.xlsx
+++ b/QSExt/Resource/AKShareDBInfo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
+    <workbookView windowWidth="20865" windowHeight="13455"/>
   </bookViews>
   <sheets>
     <sheet name="TableInfo" sheetId="1" r:id="rId1"/>
@@ -17,8 +17,8 @@
     <sheet name="ArgInfo" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TableInfo!$A$1:$F$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FactorInfo!$A$1:$F$466</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TableInfo!$A$1:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FactorInfo!$A$1:$F$478</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2831" uniqueCount="555">
   <si>
     <t>TableName</t>
   </si>
@@ -1031,6 +1031,9 @@
   </si>
   <si>
     <t>注意单位: 港元</t>
+  </si>
+  <si>
+    <t>latest</t>
   </si>
   <si>
     <t>排名</t>
@@ -3305,7 +3308,10 @@
         <v>131</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>121</v>
       </c>
       <c r="E35" t="s">
         <v>132</v>
@@ -3325,7 +3331,10 @@
         <v>136</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>120</v>
+      </c>
+      <c r="D36" t="s">
+        <v>121</v>
       </c>
       <c r="E36" t="s">
         <v>132</v>
@@ -3653,7 +3662,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F48" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F51" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -8212,7 +8221,7 @@
         <v>130</v>
       </c>
       <c r="B289" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="C289" t="s">
         <v>196</v>
@@ -8226,7 +8235,7 @@
         <v>130</v>
       </c>
       <c r="B290" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="C290" t="s">
         <v>200</v>
@@ -8240,7 +8249,7 @@
         <v>130</v>
       </c>
       <c r="B291" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="C291" t="s">
         <v>200</v>
@@ -8254,7 +8263,7 @@
         <v>130</v>
       </c>
       <c r="B292" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="C292" t="s">
         <v>200</v>
@@ -8268,7 +8277,7 @@
         <v>130</v>
       </c>
       <c r="B293" t="s">
-        <v>203</v>
+        <v>331</v>
       </c>
       <c r="C293" t="s">
         <v>200</v>
@@ -8285,7 +8294,7 @@
         <v>135</v>
       </c>
       <c r="B294" t="s">
-        <v>195</v>
+        <v>243</v>
       </c>
       <c r="C294" t="s">
         <v>196</v>
@@ -8299,7 +8308,7 @@
         <v>135</v>
       </c>
       <c r="B295" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="C295" t="s">
         <v>196</v>
@@ -8313,7 +8322,7 @@
         <v>135</v>
       </c>
       <c r="B296" t="s">
-        <v>203</v>
+        <v>248</v>
       </c>
       <c r="C296" t="s">
         <v>200</v>
@@ -8327,7 +8336,7 @@
         <v>135</v>
       </c>
       <c r="B297" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="C297" t="s">
         <v>200</v>
@@ -8341,7 +8350,7 @@
         <v>135</v>
       </c>
       <c r="B298" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="C298" t="s">
         <v>200</v>
@@ -8358,7 +8367,7 @@
         <v>135</v>
       </c>
       <c r="B299" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="C299" t="s">
         <v>200</v>
@@ -8386,7 +8395,7 @@
         <v>139</v>
       </c>
       <c r="B301" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C301" t="s">
         <v>224</v>
@@ -8400,7 +8409,7 @@
         <v>139</v>
       </c>
       <c r="B302" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C302" t="s">
         <v>196</v>
@@ -8414,7 +8423,7 @@
         <v>143</v>
       </c>
       <c r="B303" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C303" t="s">
         <v>196</v>
@@ -8428,7 +8437,7 @@
         <v>143</v>
       </c>
       <c r="B304" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C304" t="s">
         <v>196</v>
@@ -8442,7 +8451,7 @@
         <v>143</v>
       </c>
       <c r="B305" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C305" t="s">
         <v>196</v>
@@ -8456,7 +8465,7 @@
         <v>143</v>
       </c>
       <c r="B306" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C306" t="s">
         <v>196</v>
@@ -8470,7 +8479,7 @@
         <v>143</v>
       </c>
       <c r="B307" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C307" t="s">
         <v>196</v>
@@ -8484,7 +8493,7 @@
         <v>143</v>
       </c>
       <c r="B308" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C308" t="s">
         <v>196</v>
@@ -8498,7 +8507,7 @@
         <v>143</v>
       </c>
       <c r="B309" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C309" t="s">
         <v>224</v>
@@ -8512,7 +8521,7 @@
         <v>143</v>
       </c>
       <c r="B310" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C310" t="s">
         <v>196</v>
@@ -8526,7 +8535,7 @@
         <v>143</v>
       </c>
       <c r="B311" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C311" t="s">
         <v>196</v>
@@ -8540,7 +8549,7 @@
         <v>143</v>
       </c>
       <c r="B312" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C312" t="s">
         <v>196</v>
@@ -8554,7 +8563,7 @@
         <v>143</v>
       </c>
       <c r="B313" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C313" t="s">
         <v>196</v>
@@ -8568,7 +8577,7 @@
         <v>143</v>
       </c>
       <c r="B314" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C314" t="s">
         <v>196</v>
@@ -8582,7 +8591,7 @@
         <v>143</v>
       </c>
       <c r="B315" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C315" t="s">
         <v>196</v>
@@ -8596,7 +8605,7 @@
         <v>147</v>
       </c>
       <c r="B316" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C316" t="s">
         <v>196</v>
@@ -8610,7 +8619,7 @@
         <v>147</v>
       </c>
       <c r="B317" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C317" t="s">
         <v>196</v>
@@ -8624,7 +8633,7 @@
         <v>147</v>
       </c>
       <c r="B318" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C318" t="s">
         <v>196</v>
@@ -8638,7 +8647,7 @@
         <v>147</v>
       </c>
       <c r="B319" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C319" t="s">
         <v>196</v>
@@ -8652,7 +8661,7 @@
         <v>147</v>
       </c>
       <c r="B320" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C320" t="s">
         <v>196</v>
@@ -8666,7 +8675,7 @@
         <v>147</v>
       </c>
       <c r="B321" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C321" t="s">
         <v>196</v>
@@ -8680,7 +8689,7 @@
         <v>147</v>
       </c>
       <c r="B322" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C322" t="s">
         <v>196</v>
@@ -8694,7 +8703,7 @@
         <v>151</v>
       </c>
       <c r="B323" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C323" t="s">
         <v>196</v>
@@ -8708,7 +8717,7 @@
         <v>151</v>
       </c>
       <c r="B324" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C324" t="s">
         <v>196</v>
@@ -8722,7 +8731,7 @@
         <v>151</v>
       </c>
       <c r="B325" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C325" t="s">
         <v>196</v>
@@ -8736,7 +8745,7 @@
         <v>151</v>
       </c>
       <c r="B326" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C326" t="s">
         <v>196</v>
@@ -8750,7 +8759,7 @@
         <v>151</v>
       </c>
       <c r="B327" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C327" t="s">
         <v>196</v>
@@ -8764,7 +8773,7 @@
         <v>151</v>
       </c>
       <c r="B328" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C328" t="s">
         <v>196</v>
@@ -8778,7 +8787,7 @@
         <v>151</v>
       </c>
       <c r="B329" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C329" t="s">
         <v>196</v>
@@ -8792,7 +8801,7 @@
         <v>151</v>
       </c>
       <c r="B330" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C330" t="s">
         <v>196</v>
@@ -8806,7 +8815,7 @@
         <v>151</v>
       </c>
       <c r="B331" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C331" t="s">
         <v>196</v>
@@ -8820,7 +8829,7 @@
         <v>156</v>
       </c>
       <c r="B332" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C332" t="s">
         <v>200</v>
@@ -8834,7 +8843,7 @@
         <v>156</v>
       </c>
       <c r="B333" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C333" t="s">
         <v>200</v>
@@ -8848,7 +8857,7 @@
         <v>156</v>
       </c>
       <c r="B334" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C334" t="s">
         <v>224</v>
@@ -8862,7 +8871,7 @@
         <v>156</v>
       </c>
       <c r="B335" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C335" t="s">
         <v>196</v>
@@ -8876,7 +8885,7 @@
         <v>156</v>
       </c>
       <c r="B336" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C336" t="s">
         <v>196</v>
@@ -8890,7 +8899,7 @@
         <v>156</v>
       </c>
       <c r="B337" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C337" t="s">
         <v>196</v>
@@ -8904,7 +8913,7 @@
         <v>156</v>
       </c>
       <c r="B338" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C338" t="s">
         <v>224</v>
@@ -8918,7 +8927,7 @@
         <v>156</v>
       </c>
       <c r="B339" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C339" t="s">
         <v>224</v>
@@ -8932,7 +8941,7 @@
         <v>156</v>
       </c>
       <c r="B340" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C340" t="s">
         <v>196</v>
@@ -8946,7 +8955,7 @@
         <v>156</v>
       </c>
       <c r="B341" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C341" t="s">
         <v>196</v>
@@ -8960,7 +8969,7 @@
         <v>156</v>
       </c>
       <c r="B342" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C342" t="s">
         <v>200</v>
@@ -8974,7 +8983,7 @@
         <v>156</v>
       </c>
       <c r="B343" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C343" t="s">
         <v>200</v>
@@ -8988,7 +8997,7 @@
         <v>156</v>
       </c>
       <c r="B344" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C344" t="s">
         <v>224</v>
@@ -9002,7 +9011,7 @@
         <v>156</v>
       </c>
       <c r="B345" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C345" t="s">
         <v>200</v>
@@ -9016,7 +9025,7 @@
         <v>156</v>
       </c>
       <c r="B346" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C346" t="s">
         <v>200</v>
@@ -9030,7 +9039,7 @@
         <v>156</v>
       </c>
       <c r="B347" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C347" t="s">
         <v>224</v>
@@ -9044,7 +9053,7 @@
         <v>156</v>
       </c>
       <c r="B348" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C348" t="s">
         <v>200</v>
@@ -9058,7 +9067,7 @@
         <v>156</v>
       </c>
       <c r="B349" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C349" t="s">
         <v>200</v>
@@ -9072,7 +9081,7 @@
         <v>156</v>
       </c>
       <c r="B350" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C350" t="s">
         <v>200</v>
@@ -9100,7 +9109,7 @@
         <v>156</v>
       </c>
       <c r="B352" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C352" t="s">
         <v>200</v>
@@ -9114,7 +9123,7 @@
         <v>159</v>
       </c>
       <c r="B353" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C353" t="s">
         <v>196</v>
@@ -9128,7 +9137,7 @@
         <v>159</v>
       </c>
       <c r="B354" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C354" t="s">
         <v>196</v>
@@ -9142,7 +9151,7 @@
         <v>159</v>
       </c>
       <c r="B355" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C355" t="s">
         <v>196</v>
@@ -9156,7 +9165,7 @@
         <v>159</v>
       </c>
       <c r="B356" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C356" t="s">
         <v>196</v>
@@ -9170,7 +9179,7 @@
         <v>159</v>
       </c>
       <c r="B357" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C357" t="s">
         <v>200</v>
@@ -9184,7 +9193,7 @@
         <v>159</v>
       </c>
       <c r="B358" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C358" t="s">
         <v>224</v>
@@ -9198,7 +9207,7 @@
         <v>159</v>
       </c>
       <c r="B359" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C359" t="s">
         <v>224</v>
@@ -9212,7 +9221,7 @@
         <v>159</v>
       </c>
       <c r="B360" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C360" t="s">
         <v>196</v>
@@ -9240,7 +9249,7 @@
         <v>159</v>
       </c>
       <c r="B362" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C362" t="s">
         <v>196</v>
@@ -9254,7 +9263,7 @@
         <v>159</v>
       </c>
       <c r="B363" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C363" t="s">
         <v>196</v>
@@ -9268,7 +9277,7 @@
         <v>159</v>
       </c>
       <c r="B364" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C364" t="s">
         <v>196</v>
@@ -9282,7 +9291,7 @@
         <v>159</v>
       </c>
       <c r="B365" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C365" t="s">
         <v>196</v>
@@ -9296,7 +9305,7 @@
         <v>159</v>
       </c>
       <c r="B366" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C366" t="s">
         <v>196</v>
@@ -9310,7 +9319,7 @@
         <v>179</v>
       </c>
       <c r="B367" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C367" t="s">
         <v>196</v>
@@ -9324,7 +9333,7 @@
         <v>179</v>
       </c>
       <c r="B368" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C368" t="s">
         <v>200</v>
@@ -9338,7 +9347,7 @@
         <v>179</v>
       </c>
       <c r="B369" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C369" t="s">
         <v>200</v>
@@ -9352,7 +9361,7 @@
         <v>179</v>
       </c>
       <c r="B370" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C370" t="s">
         <v>200</v>
@@ -9366,7 +9375,7 @@
         <v>179</v>
       </c>
       <c r="B371" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C371" t="s">
         <v>196</v>
@@ -9380,7 +9389,7 @@
         <v>179</v>
       </c>
       <c r="B372" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C372" t="s">
         <v>196</v>
@@ -9394,7 +9403,7 @@
         <v>179</v>
       </c>
       <c r="B373" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C373" t="s">
         <v>200</v>
@@ -9408,7 +9417,7 @@
         <v>179</v>
       </c>
       <c r="B374" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C374" t="s">
         <v>196</v>
@@ -9473,7 +9482,7 @@
         <v>201</v>
       </c>
       <c r="F378" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -9599,7 +9608,7 @@
         <v>166</v>
       </c>
       <c r="B387" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C387" t="s">
         <v>224</v>
@@ -9686,7 +9695,7 @@
         <v>170</v>
       </c>
       <c r="B393" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C393" t="s">
         <v>196</v>
@@ -9700,7 +9709,7 @@
         <v>170</v>
       </c>
       <c r="B394" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C394" t="s">
         <v>200</v>
@@ -9714,7 +9723,7 @@
         <v>170</v>
       </c>
       <c r="B395" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C395" t="s">
         <v>224</v>
@@ -9728,7 +9737,7 @@
         <v>170</v>
       </c>
       <c r="B396" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C396" t="s">
         <v>200</v>
@@ -9742,7 +9751,7 @@
         <v>170</v>
       </c>
       <c r="B397" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C397" t="s">
         <v>224</v>
@@ -9756,7 +9765,7 @@
         <v>170</v>
       </c>
       <c r="B398" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C398" t="s">
         <v>200</v>
@@ -9770,7 +9779,7 @@
         <v>170</v>
       </c>
       <c r="B399" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C399" t="s">
         <v>224</v>
@@ -9784,7 +9793,7 @@
         <v>170</v>
       </c>
       <c r="B400" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C400" t="s">
         <v>200</v>
@@ -9798,7 +9807,7 @@
         <v>170</v>
       </c>
       <c r="B401" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C401" t="s">
         <v>224</v>
@@ -9826,7 +9835,7 @@
         <v>173</v>
       </c>
       <c r="B403" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C403" t="s">
         <v>196</v>
@@ -9854,7 +9863,7 @@
         <v>173</v>
       </c>
       <c r="B405" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C405" t="s">
         <v>224</v>
@@ -9882,7 +9891,7 @@
         <v>173</v>
       </c>
       <c r="B407" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C407" t="s">
         <v>224</v>
@@ -9896,7 +9905,7 @@
         <v>173</v>
       </c>
       <c r="B408" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C408" t="s">
         <v>224</v>
@@ -9910,7 +9919,7 @@
         <v>173</v>
       </c>
       <c r="B409" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C409" t="s">
         <v>224</v>
@@ -9924,7 +9933,7 @@
         <v>173</v>
       </c>
       <c r="B410" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C410" t="s">
         <v>224</v>
@@ -9938,7 +9947,7 @@
         <v>173</v>
       </c>
       <c r="B411" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C411" t="s">
         <v>224</v>
@@ -9966,7 +9975,7 @@
         <v>176</v>
       </c>
       <c r="B413" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C413" t="s">
         <v>196</v>
@@ -9980,7 +9989,7 @@
         <v>176</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C414" t="s">
         <v>200</v>
@@ -9994,7 +10003,7 @@
         <v>176</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C415" t="s">
         <v>224</v>
@@ -10008,7 +10017,7 @@
         <v>176</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C416" t="s">
         <v>200</v>
@@ -10022,7 +10031,7 @@
         <v>176</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C417" t="s">
         <v>224</v>
@@ -10036,7 +10045,7 @@
         <v>176</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C418" t="s">
         <v>200</v>
@@ -10050,7 +10059,7 @@
         <v>176</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C419" t="s">
         <v>224</v>
@@ -10064,7 +10073,7 @@
         <v>176</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C420" t="s">
         <v>200</v>
@@ -10078,7 +10087,7 @@
         <v>176</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C421" t="s">
         <v>224</v>
@@ -10092,7 +10101,7 @@
         <v>176</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C422" t="s">
         <v>200</v>
@@ -10106,7 +10115,7 @@
         <v>176</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C423" t="s">
         <v>224</v>
@@ -10120,7 +10129,7 @@
         <v>176</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C424" t="s">
         <v>200</v>
@@ -10134,7 +10143,7 @@
         <v>176</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C425" t="s">
         <v>224</v>
@@ -10148,7 +10157,7 @@
         <v>176</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C426" t="s">
         <v>200</v>
@@ -10162,7 +10171,7 @@
         <v>176</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C427" t="s">
         <v>224</v>
@@ -10176,7 +10185,7 @@
         <v>176</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C428" t="s">
         <v>200</v>
@@ -10190,7 +10199,7 @@
         <v>176</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C429" t="s">
         <v>224</v>
@@ -10323,7 +10332,7 @@
         <v>124</v>
       </c>
       <c r="B437" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C437" t="s">
         <v>196</v>
@@ -10332,7 +10341,7 @@
         <v>201</v>
       </c>
       <c r="F437" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="438" spans="1:6">
@@ -10340,7 +10349,7 @@
         <v>124</v>
       </c>
       <c r="B438" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C438" t="s">
         <v>196</v>
@@ -10349,7 +10358,7 @@
         <v>201</v>
       </c>
       <c r="F438" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -10357,7 +10366,7 @@
         <v>126</v>
       </c>
       <c r="B439" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C439" t="s">
         <v>196</v>
@@ -10385,7 +10394,7 @@
         <v>126</v>
       </c>
       <c r="B441" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C441" t="s">
         <v>196</v>
@@ -10399,7 +10408,7 @@
         <v>126</v>
       </c>
       <c r="B442" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C442" t="s">
         <v>196</v>
@@ -10413,7 +10422,7 @@
         <v>126</v>
       </c>
       <c r="B443" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C443" t="s">
         <v>196</v>
@@ -10553,7 +10562,7 @@
         <v>126</v>
       </c>
       <c r="B453" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C453" t="s">
         <v>200</v>
@@ -10567,7 +10576,7 @@
         <v>126</v>
       </c>
       <c r="B454" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C454" t="s">
         <v>200</v>
@@ -10632,7 +10641,7 @@
         <v>201</v>
       </c>
       <c r="F458" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -10649,7 +10658,7 @@
         <v>201</v>
       </c>
       <c r="F459" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="460" spans="1:6">
@@ -10666,7 +10675,7 @@
         <v>201</v>
       </c>
       <c r="F460" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="461" spans="1:6">
@@ -10739,7 +10748,7 @@
         <v>201</v>
       </c>
       <c r="F465" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -10756,7 +10765,7 @@
         <v>201</v>
       </c>
       <c r="F466" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -10764,7 +10773,7 @@
         <v>184</v>
       </c>
       <c r="B467" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C467" t="s">
         <v>196</v>
@@ -10778,7 +10787,7 @@
         <v>184</v>
       </c>
       <c r="B468" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C468" t="s">
         <v>196</v>
@@ -10792,7 +10801,7 @@
         <v>184</v>
       </c>
       <c r="B469" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C469" t="s">
         <v>200</v>
@@ -10834,7 +10843,7 @@
         <v>189</v>
       </c>
       <c r="B472" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C472" t="s">
         <v>224</v>
@@ -10848,7 +10857,7 @@
         <v>189</v>
       </c>
       <c r="B473" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C473" t="s">
         <v>200</v>
@@ -10862,7 +10871,7 @@
         <v>189</v>
       </c>
       <c r="B474" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C474" t="s">
         <v>200</v>
@@ -10876,7 +10885,7 @@
         <v>189</v>
       </c>
       <c r="B475" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C475" t="s">
         <v>200</v>
@@ -10890,7 +10899,7 @@
         <v>189</v>
       </c>
       <c r="B476" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C476" t="s">
         <v>200</v>
@@ -10928,7 +10937,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F466" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F478" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10957,7 +10966,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C1" t="s">
         <v>192</v>
@@ -10966,10 +10975,10 @@
         <v>193</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G1" t="s">
         <v>5</v>
@@ -10980,7 +10989,7 @@
         <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C2" t="s">
         <v>323</v>
@@ -10992,7 +11001,7 @@
         <v>603777</v>
       </c>
       <c r="G2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -11000,22 +11009,22 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C3" t="s">
         <v>323</v>
       </c>
       <c r="D3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -11023,19 +11032,19 @@
         <v>20</v>
       </c>
       <c r="B4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C4" t="s">
         <v>323</v>
       </c>
       <c r="D4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E4" s="1">
         <v>20210301</v>
       </c>
       <c r="G4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -11043,19 +11052,19 @@
         <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C5" t="s">
         <v>323</v>
       </c>
       <c r="D5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E5" s="1">
         <v>20210616</v>
       </c>
       <c r="G5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -11063,19 +11072,19 @@
         <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
         <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -11083,7 +11092,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C7" t="s">
         <v>323</v>
@@ -11100,7 +11109,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C8" t="s">
         <v>323</v>
@@ -11112,7 +11121,7 @@
         <v>603777</v>
       </c>
       <c r="G8" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -11120,19 +11129,19 @@
         <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C9" t="s">
         <v>323</v>
       </c>
       <c r="D9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E9" s="1">
         <v>20210301</v>
       </c>
       <c r="G9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -11140,19 +11149,19 @@
         <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C10" t="s">
         <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E10" s="1">
         <v>20210616</v>
       </c>
       <c r="G10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -11160,19 +11169,19 @@
         <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C11" t="s">
         <v>323</v>
       </c>
       <c r="D11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -11180,7 +11189,7 @@
         <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C12" t="s">
         <v>323</v>
@@ -11192,7 +11201,7 @@
         <v>603777</v>
       </c>
       <c r="G12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -11200,19 +11209,19 @@
         <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C13" t="s">
         <v>323</v>
       </c>
       <c r="D13" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E13" s="1">
         <v>20210301</v>
       </c>
       <c r="G13" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -11220,19 +11229,19 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C14" t="s">
         <v>323</v>
       </c>
       <c r="D14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E14" s="1">
         <v>20210616</v>
       </c>
       <c r="G14" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -11240,7 +11249,7 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C15" t="s">
         <v>323</v>
@@ -11249,7 +11258,7 @@
         <v>226</v>
       </c>
       <c r="G15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -11257,22 +11266,22 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C16" t="s">
         <v>323</v>
       </c>
       <c r="D16" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F16" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G16" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -11280,19 +11289,19 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C17" t="s">
         <v>323</v>
       </c>
       <c r="D17" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F17" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G17" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -11300,7 +11309,7 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C18" t="s">
         <v>323</v>
@@ -11312,7 +11321,7 @@
         <v>603777</v>
       </c>
       <c r="G18" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -11320,19 +11329,19 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C19" t="s">
         <v>323</v>
       </c>
       <c r="D19" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E19" s="1">
         <v>20210301</v>
       </c>
       <c r="G19" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -11340,19 +11349,19 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C20" t="s">
         <v>323</v>
       </c>
       <c r="D20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E20" s="1">
         <v>20210616</v>
       </c>
       <c r="G20" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -11360,22 +11369,22 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C21" t="s">
         <v>323</v>
       </c>
       <c r="D21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F21" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G21" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -11383,19 +11392,19 @@
         <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C22" t="s">
         <v>323</v>
       </c>
       <c r="D22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -11403,7 +11412,7 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C23" t="s">
         <v>323</v>
@@ -11415,7 +11424,7 @@
         <v>603777</v>
       </c>
       <c r="G23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -11423,19 +11432,19 @@
         <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C24" t="s">
         <v>323</v>
       </c>
       <c r="D24" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E24" s="1">
         <v>20210301</v>
       </c>
       <c r="G24" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -11443,19 +11452,19 @@
         <v>35</v>
       </c>
       <c r="B25" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C25" t="s">
         <v>323</v>
       </c>
       <c r="D25" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E25" s="1">
         <v>20210616</v>
       </c>
       <c r="G25" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -11463,7 +11472,7 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C26" t="s">
         <v>323</v>
@@ -11472,7 +11481,7 @@
         <v>226</v>
       </c>
       <c r="G26" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -11480,7 +11489,7 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C27" t="s">
         <v>323</v>
@@ -11489,7 +11498,7 @@
         <v>197</v>
       </c>
       <c r="G27" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -11497,7 +11506,7 @@
         <v>41</v>
       </c>
       <c r="B28" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C28" t="s">
         <v>323</v>
@@ -11506,7 +11515,7 @@
         <v>226</v>
       </c>
       <c r="G28" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -11514,16 +11523,16 @@
         <v>41</v>
       </c>
       <c r="B29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D29" t="s">
         <v>197</v>
       </c>
       <c r="G29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -11531,7 +11540,7 @@
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C30" t="s">
         <v>323</v>
@@ -11540,7 +11549,7 @@
         <v>226</v>
       </c>
       <c r="G30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -11548,7 +11557,7 @@
         <v>57</v>
       </c>
       <c r="B31" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C31" t="s">
         <v>323</v>
@@ -11557,7 +11566,7 @@
         <v>226</v>
       </c>
       <c r="G31" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -11565,16 +11574,16 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C32" t="s">
         <v>323</v>
       </c>
       <c r="D32" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G32" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -11582,16 +11591,16 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C33" t="s">
         <v>323</v>
       </c>
       <c r="D33" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G33" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -11608,7 +11617,7 @@
         <v>197</v>
       </c>
       <c r="G34" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -11625,7 +11634,7 @@
         <v>197</v>
       </c>
       <c r="G35" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -11633,22 +11642,22 @@
         <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C36" t="s">
         <v>323</v>
       </c>
       <c r="D36" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F36" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G36" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -11656,22 +11665,22 @@
         <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C37" t="s">
         <v>323</v>
       </c>
       <c r="D37" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F37" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G37" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -11679,22 +11688,22 @@
         <v>89</v>
       </c>
       <c r="B38" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C38" t="s">
         <v>323</v>
       </c>
       <c r="D38" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F38" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G38" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -11702,7 +11711,7 @@
         <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C39" t="s">
         <v>323</v>
@@ -11711,10 +11720,10 @@
         <v>226</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G39" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -11722,19 +11731,19 @@
         <v>93</v>
       </c>
       <c r="B40" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C40" t="s">
         <v>323</v>
       </c>
       <c r="D40" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E40" s="1">
         <v>20210301</v>
       </c>
       <c r="G40" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -11742,19 +11751,19 @@
         <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C41" t="s">
         <v>323</v>
       </c>
       <c r="D41" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E41" s="1">
         <v>20210616</v>
       </c>
       <c r="G41" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -11762,22 +11771,22 @@
         <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C42" t="s">
         <v>323</v>
       </c>
       <c r="D42" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F42" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G42" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -11785,19 +11794,19 @@
         <v>93</v>
       </c>
       <c r="B43" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C43" t="s">
         <v>323</v>
       </c>
       <c r="D43" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F43" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G43" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -11805,7 +11814,7 @@
         <v>101</v>
       </c>
       <c r="B44" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C44" t="s">
         <v>323</v>
@@ -11814,10 +11823,10 @@
         <v>226</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G44" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -11825,22 +11834,22 @@
         <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C45" t="s">
         <v>323</v>
       </c>
       <c r="D45" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F45" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G45" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -11848,7 +11857,7 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C46" t="s">
         <v>323</v>
@@ -11857,10 +11866,10 @@
         <v>226</v>
       </c>
       <c r="E46" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G46" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -11868,22 +11877,22 @@
         <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C47" t="s">
         <v>323</v>
       </c>
       <c r="D47" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E47" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F47" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G47" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -11891,19 +11900,19 @@
         <v>105</v>
       </c>
       <c r="B48" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C48" t="s">
         <v>323</v>
       </c>
       <c r="D48" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E48" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G48" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -11911,19 +11920,19 @@
         <v>105</v>
       </c>
       <c r="B49" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C49" t="s">
         <v>323</v>
       </c>
       <c r="D49" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E49" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G49" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -11931,19 +11940,19 @@
         <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C50" t="s">
         <v>323</v>
       </c>
       <c r="D50" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F50" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G50" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -11951,7 +11960,7 @@
         <v>110</v>
       </c>
       <c r="B51" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C51" t="s">
         <v>323</v>
@@ -11960,10 +11969,10 @@
         <v>226</v>
       </c>
       <c r="E51" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G51" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -11971,22 +11980,22 @@
         <v>110</v>
       </c>
       <c r="B52" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C52" t="s">
         <v>323</v>
       </c>
       <c r="D52" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E52" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F52" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G52" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -11994,19 +12003,19 @@
         <v>110</v>
       </c>
       <c r="B53" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C53" t="s">
         <v>323</v>
       </c>
       <c r="D53" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F53" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G53" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -12014,19 +12023,19 @@
         <v>110</v>
       </c>
       <c r="B54" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C54" t="s">
         <v>323</v>
       </c>
       <c r="D54" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E54" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G54" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -12034,19 +12043,19 @@
         <v>110</v>
       </c>
       <c r="B55" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C55" t="s">
         <v>323</v>
       </c>
       <c r="D55" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E55" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G55" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -12054,7 +12063,7 @@
         <v>130</v>
       </c>
       <c r="B56" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C56" t="s">
         <v>323</v>
@@ -12063,10 +12072,10 @@
         <v>226</v>
       </c>
       <c r="E56" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G56" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -12074,7 +12083,7 @@
         <v>135</v>
       </c>
       <c r="B57" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C57" t="s">
         <v>323</v>
@@ -12083,10 +12092,10 @@
         <v>226</v>
       </c>
       <c r="E57" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G57" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -12094,7 +12103,7 @@
         <v>139</v>
       </c>
       <c r="B58" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C58" t="s">
         <v>323</v>
@@ -12103,10 +12112,10 @@
         <v>226</v>
       </c>
       <c r="E58" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G58" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -12114,7 +12123,7 @@
         <v>143</v>
       </c>
       <c r="B59" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C59" t="s">
         <v>323</v>
@@ -12123,10 +12132,10 @@
         <v>226</v>
       </c>
       <c r="E59" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G59" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -12134,7 +12143,7 @@
         <v>147</v>
       </c>
       <c r="B60" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C60" t="s">
         <v>323</v>
@@ -12143,10 +12152,10 @@
         <v>226</v>
       </c>
       <c r="E60" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G60" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -12154,7 +12163,7 @@
         <v>151</v>
       </c>
       <c r="B61" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C61" t="s">
         <v>323</v>
@@ -12163,10 +12172,10 @@
         <v>226</v>
       </c>
       <c r="E61" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G61" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -12174,7 +12183,7 @@
         <v>156</v>
       </c>
       <c r="B62" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C62" t="s">
         <v>323</v>
@@ -12183,10 +12192,10 @@
         <v>226</v>
       </c>
       <c r="E62" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G62" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -12194,7 +12203,7 @@
         <v>159</v>
       </c>
       <c r="B63" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C63" t="s">
         <v>323</v>
@@ -12203,10 +12212,10 @@
         <v>226</v>
       </c>
       <c r="E63" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G63" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -12214,7 +12223,7 @@
         <v>170</v>
       </c>
       <c r="B64" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C64" t="s">
         <v>323</v>
@@ -12223,10 +12232,10 @@
         <v>226</v>
       </c>
       <c r="E64" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G64" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -12234,7 +12243,7 @@
         <v>173</v>
       </c>
       <c r="B65" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C65" t="s">
         <v>323</v>
@@ -12243,10 +12252,10 @@
         <v>226</v>
       </c>
       <c r="E65" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G65" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -12254,7 +12263,7 @@
         <v>176</v>
       </c>
       <c r="B66" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C66" t="s">
         <v>323</v>
@@ -12263,10 +12272,10 @@
         <v>226</v>
       </c>
       <c r="E66" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G66" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -12274,7 +12283,7 @@
         <v>118</v>
       </c>
       <c r="B67" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C67" t="s">
         <v>323</v>
@@ -12283,10 +12292,10 @@
         <v>226</v>
       </c>
       <c r="E67" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G67" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -12294,19 +12303,19 @@
         <v>118</v>
       </c>
       <c r="B68" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C68" t="s">
         <v>323</v>
       </c>
       <c r="D68" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F68" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G68" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -12314,7 +12323,7 @@
         <v>124</v>
       </c>
       <c r="B69" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C69" t="s">
         <v>323</v>
@@ -12323,10 +12332,10 @@
         <v>226</v>
       </c>
       <c r="E69" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G69" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -12334,22 +12343,22 @@
         <v>124</v>
       </c>
       <c r="B70" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C70" t="s">
         <v>323</v>
       </c>
       <c r="D70" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F70" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G70" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -12357,7 +12366,7 @@
         <v>179</v>
       </c>
       <c r="B71" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C71" t="s">
         <v>323</v>
@@ -12366,10 +12375,10 @@
         <v>226</v>
       </c>
       <c r="E71" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G71" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -12377,22 +12386,22 @@
         <v>179</v>
       </c>
       <c r="B72" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C72" t="s">
         <v>323</v>
       </c>
       <c r="D72" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E72" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F72" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G72" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -12400,7 +12409,7 @@
         <v>184</v>
       </c>
       <c r="B73" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C73" t="s">
         <v>323</v>
@@ -12409,10 +12418,10 @@
         <v>226</v>
       </c>
       <c r="E73" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G73" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -12420,22 +12429,22 @@
         <v>184</v>
       </c>
       <c r="B74" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C74" t="s">
         <v>323</v>
       </c>
       <c r="D74" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E74" t="s">
+        <v>549</v>
+      </c>
+      <c r="F74" t="s">
+        <v>550</v>
+      </c>
+      <c r="G74" t="s">
         <v>548</v>
-      </c>
-      <c r="F74" t="s">
-        <v>549</v>
-      </c>
-      <c r="G74" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -12443,7 +12452,7 @@
         <v>186</v>
       </c>
       <c r="B75" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C75" t="s">
         <v>323</v>
@@ -12452,10 +12461,10 @@
         <v>226</v>
       </c>
       <c r="E75" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G75" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -12463,22 +12472,22 @@
         <v>186</v>
       </c>
       <c r="B76" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C76" t="s">
         <v>323</v>
       </c>
       <c r="D76" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E76" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F76" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G76" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -12486,7 +12495,7 @@
         <v>189</v>
       </c>
       <c r="B77" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C77" t="s">
         <v>323</v>
@@ -12495,10 +12504,10 @@
         <v>226</v>
       </c>
       <c r="E77" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G77" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -12506,22 +12515,22 @@
         <v>189</v>
       </c>
       <c r="B78" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C78" t="s">
         <v>323</v>
       </c>
       <c r="D78" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E78" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F78" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G78" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
